--- a/server/templates/VQ-template.xlsx
+++ b/server/templates/VQ-template.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="255">
   <si>
     <t xml:space="preserve">Vendor:  </t>
   </si>
@@ -652,9 +652,6 @@
   </si>
   <si>
     <t>pc</t>
-  </si>
-  <si>
-    <t>Refer to 47674</t>
   </si>
   <si>
     <t>PCBA</t>
@@ -2913,7 +2910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="399">
+  <cellXfs count="401">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3580,6 +3577,14 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4943,7 +4948,7 @@
     <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="10" customWidth="1"/>
     <col min="4" max="4" width="13.375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="176" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="178" customWidth="1"/>
     <col min="6" max="7" width="12.375" style="10" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="10" customWidth="1"/>
     <col min="9" max="9" width="12.625" style="10" customWidth="1"/>
@@ -4953,821 +4958,821 @@
   </cols>
   <sheetData>
     <row r="1" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="324"/>
-    </row>
-    <row r="2" s="174" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A2" s="178"/>
-      <c r="B2" s="179" t="s">
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="326"/>
+    </row>
+    <row r="2" s="176" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
+      <c r="A2" s="180"/>
+      <c r="B2" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="C2" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="180"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="179" t="s">
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="182" t="s">
+      <c r="H2" s="184" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="182"/>
-    </row>
-    <row r="3" s="174" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A3" s="178"/>
-      <c r="B3" s="179" t="s">
+      <c r="I2" s="184"/>
+    </row>
+    <row r="3" s="176" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
+      <c r="A3" s="180"/>
+      <c r="B3" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="183">
+      <c r="C3" s="185">
         <v>47712</v>
       </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="179" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="181" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="184">
+      <c r="H3" s="186">
         <v>45937</v>
       </c>
-      <c r="I3" s="184"/>
-    </row>
-    <row r="4" s="174" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A4" s="178"/>
-      <c r="B4" s="179" t="s">
+      <c r="I3" s="186"/>
+    </row>
+    <row r="4" s="176" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
+      <c r="A4" s="180"/>
+      <c r="B4" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="183" t="s">
+      <c r="C4" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="183"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="186" t="s">
+      <c r="D4" s="185"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="188" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="189">
         <v>5</v>
       </c>
-      <c r="I4" s="187"/>
-    </row>
-    <row r="5" s="174" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A5" s="178"/>
-      <c r="B5" s="179" t="s">
+      <c r="I4" s="189"/>
+    </row>
+    <row r="5" s="176" customFormat="1" ht="19.5" customHeight="1" spans="1:9">
+      <c r="A5" s="180"/>
+      <c r="B5" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="182">
+      <c r="C5" s="184">
         <v>0</v>
       </c>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="179" t="s">
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
     </row>
     <row r="7" ht="17.4" spans="1:9">
-      <c r="A7" s="188" t="s">
+      <c r="A7" s="190" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="188"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="188"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="189"/>
-      <c r="B8" s="189"/>
-      <c r="C8" s="189"/>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
-      <c r="G8" s="189"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="189"/>
+      <c r="A8" s="191"/>
+      <c r="B8" s="191"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
-      <c r="A9" s="190" t="s">
+      <c r="A9" s="192" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
-      <c r="D9" s="189"/>
-      <c r="E9" s="191"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="193"/>
     </row>
     <row r="10" ht="78.75" spans="1:9">
-      <c r="A10" s="192" t="s">
+      <c r="A10" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="193" t="s">
+      <c r="B10" s="195" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="193"/>
-      <c r="D10" s="193"/>
-      <c r="E10" s="192" t="s">
+      <c r="C10" s="195"/>
+      <c r="D10" s="195"/>
+      <c r="E10" s="194" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="193" t="s">
+      <c r="F10" s="195" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="194" t="s">
+      <c r="G10" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="194" t="s">
+      <c r="H10" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="325" t="s">
+      <c r="I10" s="327" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A11" s="195" t="s">
+      <c r="A11" s="197" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="196" t="s">
+      <c r="B11" s="198" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="197"/>
-      <c r="D11" s="198"/>
-      <c r="E11" s="199">
+      <c r="C11" s="199"/>
+      <c r="D11" s="200"/>
+      <c r="E11" s="201">
         <v>2500</v>
       </c>
-      <c r="F11" s="200">
+      <c r="F11" s="202">
         <v>1</v>
       </c>
-      <c r="G11" s="201">
+      <c r="G11" s="203">
         <f>'Body Cost Breakdown'!F23</f>
         <v>121.63</v>
       </c>
-      <c r="H11" s="202">
+      <c r="H11" s="204">
         <f>G11*F11</f>
         <v>121.63</v>
       </c>
-      <c r="I11" s="326"/>
+      <c r="I11" s="328"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="196" t="s">
+      <c r="B12" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="197"/>
-      <c r="D12" s="198"/>
-      <c r="E12" s="199">
+      <c r="C12" s="199"/>
+      <c r="D12" s="200"/>
+      <c r="E12" s="201">
         <v>2500</v>
       </c>
-      <c r="F12" s="200">
+      <c r="F12" s="202">
         <v>3</v>
       </c>
-      <c r="G12" s="204">
+      <c r="G12" s="206">
         <v>0.449</v>
       </c>
-      <c r="H12" s="205">
+      <c r="H12" s="207">
         <f t="shared" ref="H12:H16" si="0">G12*F12</f>
         <v>1.347</v>
       </c>
-      <c r="I12" s="327"/>
+      <c r="I12" s="329"/>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A13" s="203"/>
-      <c r="B13" s="196"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="199"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="327"/>
+      <c r="A13" s="205"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="329"/>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A14" s="203"/>
-      <c r="B14" s="196"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="199"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="327"/>
+      <c r="A14" s="205"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="201"/>
+      <c r="F14" s="202"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="329"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A15" s="203"/>
-      <c r="B15" s="196"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="204"/>
-      <c r="H15" s="205">
+      <c r="A15" s="205"/>
+      <c r="B15" s="198"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="202"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="207">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="327"/>
+      <c r="I15" s="329"/>
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A16" s="207"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="211"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="213"/>
-      <c r="H16" s="214">
+      <c r="A16" s="209"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="213"/>
+      <c r="F16" s="214"/>
+      <c r="G16" s="215"/>
+      <c r="H16" s="216">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="328"/>
+      <c r="I16" s="330"/>
     </row>
     <row r="17" ht="15.6" spans="1:9">
-      <c r="A17" s="189"/>
-      <c r="B17" s="189"/>
-      <c r="C17" s="189"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="191"/>
-      <c r="G17" s="215"/>
-      <c r="H17" s="215"/>
-      <c r="I17" s="329">
+      <c r="A17" s="191"/>
+      <c r="B17" s="191"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
+      <c r="E17" s="193"/>
+      <c r="G17" s="217"/>
+      <c r="H17" s="217"/>
+      <c r="I17" s="331">
         <f>SUM(H11:H16)</f>
         <v>122.977</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="189"/>
-      <c r="B18" s="189"/>
-      <c r="C18" s="189"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="191"/>
-      <c r="G18" s="215"/>
-      <c r="H18" s="215"/>
-      <c r="I18" s="330">
+      <c r="A18" s="191"/>
+      <c r="B18" s="191"/>
+      <c r="C18" s="191"/>
+      <c r="D18" s="191"/>
+      <c r="E18" s="193"/>
+      <c r="G18" s="217"/>
+      <c r="H18" s="217"/>
+      <c r="I18" s="332">
         <f>I17/$G$68</f>
         <v>0.726931374461908</v>
       </c>
     </row>
     <row r="19" ht="15.6" spans="1:9">
-      <c r="A19" s="189"/>
-      <c r="B19" s="189"/>
-      <c r="C19" s="189"/>
-      <c r="D19" s="189"/>
-      <c r="E19" s="191"/>
-      <c r="G19" s="215"/>
-      <c r="H19" s="215"/>
-      <c r="I19" s="331"/>
+      <c r="A19" s="191"/>
+      <c r="B19" s="191"/>
+      <c r="C19" s="191"/>
+      <c r="D19" s="191"/>
+      <c r="E19" s="193"/>
+      <c r="G19" s="217"/>
+      <c r="H19" s="217"/>
+      <c r="I19" s="333"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="189"/>
-      <c r="B20" s="189"/>
-      <c r="C20" s="189"/>
-      <c r="D20" s="189"/>
-      <c r="E20" s="191"/>
-      <c r="G20" s="215"/>
-      <c r="H20" s="216"/>
+      <c r="A20" s="191"/>
+      <c r="B20" s="191"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="193"/>
+      <c r="G20" s="217"/>
+      <c r="H20" s="218"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" ht="15.6" spans="1:9">
-      <c r="A21" s="217" t="s">
+      <c r="A21" s="219" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="218"/>
-      <c r="C21" s="218"/>
-      <c r="D21" s="218"/>
-      <c r="E21" s="191"/>
-      <c r="F21" s="219"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="220"/>
-      <c r="I21" s="332"/>
+      <c r="B21" s="220"/>
+      <c r="C21" s="220"/>
+      <c r="D21" s="220"/>
+      <c r="E21" s="193"/>
+      <c r="F21" s="221"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="334"/>
     </row>
     <row r="22" ht="31.95" spans="1:9">
-      <c r="A22" s="192" t="s">
+      <c r="A22" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="221" t="s">
+      <c r="B22" s="223" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="222" t="s">
+      <c r="C22" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="223"/>
-      <c r="E22" s="224" t="s">
+      <c r="D22" s="225"/>
+      <c r="E22" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="224" t="s">
+      <c r="F22" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="194" t="s">
+      <c r="G22" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="194" t="s">
+      <c r="H22" s="196" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A23" s="225"/>
-      <c r="B23" s="226" t="s">
+      <c r="A23" s="227"/>
+      <c r="B23" s="228" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="227" t="s">
+      <c r="C23" s="229" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="228"/>
-      <c r="E23" s="199">
+      <c r="D23" s="230"/>
+      <c r="E23" s="201">
         <v>2500</v>
       </c>
-      <c r="F23" s="229">
+      <c r="F23" s="231">
         <v>1</v>
       </c>
-      <c r="G23" s="230">
+      <c r="G23" s="232">
         <v>11.378275862069</v>
       </c>
-      <c r="H23" s="231">
+      <c r="H23" s="233">
         <f t="shared" ref="H23:H33" si="1">ROUND(F23*G23,2)</f>
         <v>11.38</v>
       </c>
       <c r="I23" s="3"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A24" s="232"/>
-      <c r="B24" s="233" t="s">
+      <c r="A24" s="234"/>
+      <c r="B24" s="235" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="227" t="s">
+      <c r="C24" s="229" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="228"/>
-      <c r="E24" s="199">
+      <c r="D24" s="230"/>
+      <c r="E24" s="201">
         <v>2500</v>
       </c>
-      <c r="F24" s="229">
+      <c r="F24" s="231">
         <v>1</v>
       </c>
-      <c r="G24" s="230">
+      <c r="G24" s="232">
         <v>5.8611724137931</v>
       </c>
-      <c r="H24" s="231">
+      <c r="H24" s="233">
         <f t="shared" si="1"/>
         <v>5.86</v>
       </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A25" s="232"/>
-      <c r="B25" s="233" t="s">
+      <c r="A25" s="234"/>
+      <c r="B25" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="227" t="s">
+      <c r="C25" s="229" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="228"/>
-      <c r="E25" s="199">
+      <c r="D25" s="230"/>
+      <c r="E25" s="201">
         <v>2500</v>
       </c>
-      <c r="F25" s="229">
+      <c r="F25" s="231">
         <v>2</v>
       </c>
-      <c r="G25" s="230">
+      <c r="G25" s="232">
         <v>1.3813793103448</v>
       </c>
-      <c r="H25" s="231">
+      <c r="H25" s="233">
         <f t="shared" si="1"/>
         <v>2.76</v>
       </c>
       <c r="I25" s="3"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A26" s="232"/>
-      <c r="B26" s="233" t="s">
+      <c r="A26" s="234"/>
+      <c r="B26" s="235" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="227" t="s">
+      <c r="C26" s="229" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="228"/>
-      <c r="E26" s="199">
+      <c r="D26" s="230"/>
+      <c r="E26" s="201">
         <v>2500</v>
       </c>
-      <c r="F26" s="229">
+      <c r="F26" s="231">
         <v>1</v>
       </c>
-      <c r="G26" s="230">
+      <c r="G26" s="232">
         <v>0.88</v>
       </c>
-      <c r="H26" s="231">
+      <c r="H26" s="233">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
       <c r="I26" s="3"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A27" s="232"/>
-      <c r="B27" s="233" t="s">
+      <c r="A27" s="234"/>
+      <c r="B27" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="227"/>
-      <c r="D27" s="228"/>
-      <c r="E27" s="199">
+      <c r="C27" s="229"/>
+      <c r="D27" s="230"/>
+      <c r="E27" s="201">
         <v>2500</v>
       </c>
-      <c r="F27" s="229">
+      <c r="F27" s="231">
         <v>4</v>
       </c>
-      <c r="G27" s="230">
+      <c r="G27" s="232">
         <v>0.204303448275862</v>
       </c>
-      <c r="H27" s="231">
+      <c r="H27" s="233">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
       <c r="I27" s="3"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A28" s="232"/>
-      <c r="B28" s="233" t="s">
+      <c r="A28" s="234"/>
+      <c r="B28" s="235" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="227"/>
-      <c r="D28" s="228"/>
-      <c r="E28" s="199">
+      <c r="C28" s="229"/>
+      <c r="D28" s="230"/>
+      <c r="E28" s="201">
         <v>2500</v>
       </c>
-      <c r="F28" s="229">
+      <c r="F28" s="231">
         <v>4</v>
       </c>
-      <c r="G28" s="230">
+      <c r="G28" s="232">
         <v>0.0719540229885057</v>
       </c>
-      <c r="H28" s="231">
+      <c r="H28" s="233">
         <f t="shared" si="1"/>
         <v>0.29</v>
       </c>
       <c r="I28" s="3"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A29" s="232"/>
-      <c r="B29" s="233" t="s">
+      <c r="A29" s="234"/>
+      <c r="B29" s="235" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="227"/>
-      <c r="D29" s="228"/>
-      <c r="E29" s="199">
+      <c r="C29" s="229"/>
+      <c r="D29" s="230"/>
+      <c r="E29" s="201">
         <v>2500</v>
       </c>
-      <c r="F29" s="229">
+      <c r="F29" s="231">
         <v>2</v>
       </c>
-      <c r="G29" s="230">
+      <c r="G29" s="232">
         <v>0.54689655172414</v>
       </c>
-      <c r="H29" s="231">
+      <c r="H29" s="233">
         <f t="shared" si="1"/>
         <v>1.09</v>
       </c>
       <c r="I29" s="3"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A30" s="232"/>
-      <c r="B30" s="233" t="s">
+      <c r="A30" s="234"/>
+      <c r="B30" s="235" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="227"/>
-      <c r="D30" s="228"/>
-      <c r="E30" s="199">
+      <c r="C30" s="229"/>
+      <c r="D30" s="230"/>
+      <c r="E30" s="201">
         <v>2500</v>
       </c>
-      <c r="F30" s="229">
+      <c r="F30" s="231">
         <v>1</v>
       </c>
-      <c r="G30" s="230">
+      <c r="G30" s="232">
         <v>0.84</v>
       </c>
-      <c r="H30" s="231">
+      <c r="H30" s="233">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
       <c r="I30" s="3"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A31" s="232"/>
-      <c r="B31" s="233" t="s">
+      <c r="A31" s="234"/>
+      <c r="B31" s="235" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="227"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="199">
+      <c r="C31" s="229"/>
+      <c r="D31" s="230"/>
+      <c r="E31" s="201">
         <v>2500</v>
       </c>
-      <c r="F31" s="229">
+      <c r="F31" s="231">
         <v>1</v>
       </c>
-      <c r="G31" s="230">
+      <c r="G31" s="232">
         <v>0.05</v>
       </c>
-      <c r="H31" s="231">
+      <c r="H31" s="233">
         <f t="shared" si="1"/>
         <v>0.05</v>
       </c>
       <c r="I31" s="3"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A32" s="232"/>
-      <c r="B32" s="233"/>
-      <c r="C32" s="227"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="199"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="230"/>
-      <c r="H32" s="231">
+      <c r="A32" s="234"/>
+      <c r="B32" s="235"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="230"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="231"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="233">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="3"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A33" s="232"/>
-      <c r="B33" s="234"/>
-      <c r="C33" s="235"/>
-      <c r="D33" s="236"/>
-      <c r="E33" s="199"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="237"/>
+      <c r="A33" s="234"/>
+      <c r="B33" s="236"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="231"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="239"/>
       <c r="I33" s="3"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A34" s="232"/>
-      <c r="B34" s="226" t="s">
+      <c r="A34" s="234"/>
+      <c r="B34" s="228" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="235"/>
-      <c r="D34" s="236"/>
-      <c r="E34" s="199"/>
-      <c r="F34" s="238">
+      <c r="C34" s="237"/>
+      <c r="D34" s="238"/>
+      <c r="E34" s="201"/>
+      <c r="F34" s="240">
         <v>1</v>
       </c>
-      <c r="G34" s="239">
+      <c r="G34" s="241">
         <v>0.3</v>
       </c>
-      <c r="H34" s="237">
+      <c r="H34" s="239">
         <f>ROUND(F34*G34,2)</f>
         <v>0.3</v>
       </c>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="240"/>
-      <c r="B35" s="241" t="s">
+      <c r="A35" s="242"/>
+      <c r="B35" s="243" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="227"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="199"/>
-      <c r="F35" s="238">
+      <c r="C35" s="229"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="201"/>
+      <c r="F35" s="240">
         <v>1</v>
       </c>
-      <c r="G35" s="242">
+      <c r="G35" s="244">
         <v>4.02913043478261</v>
       </c>
-      <c r="H35" s="237">
+      <c r="H35" s="239">
         <f>G35</f>
         <v>4.02913043478261</v>
       </c>
       <c r="I35" s="3"/>
     </row>
     <row r="36" ht="15.6" spans="1:9">
-      <c r="A36" s="243" t="s">
+      <c r="A36" s="245" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="244"/>
-      <c r="C36" s="244"/>
-      <c r="D36" s="244"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="246"/>
-      <c r="G36" s="247">
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="247"/>
+      <c r="F36" s="248"/>
+      <c r="G36" s="249">
         <v>0.12</v>
       </c>
-      <c r="H36" s="248">
+      <c r="H36" s="250">
         <f>ROUND((SUM(H23:H35)*G36),2)</f>
         <v>3.4</v>
       </c>
-      <c r="I36" s="333">
+      <c r="I36" s="335">
         <f>SUM(H23:H36)</f>
         <v>31.6991304347826</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="189"/>
-      <c r="B37" s="189"/>
-      <c r="C37" s="189"/>
-      <c r="D37" s="189"/>
-      <c r="E37" s="191"/>
-      <c r="I37" s="330">
+      <c r="A37" s="191"/>
+      <c r="B37" s="191"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
+      <c r="E37" s="193"/>
+      <c r="I37" s="332">
         <f>I36/$G$68</f>
         <v>0.187377253114028</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="189"/>
-      <c r="B38" s="189"/>
-      <c r="C38" s="189"/>
-      <c r="D38" s="189"/>
-      <c r="E38" s="191"/>
+      <c r="A38" s="191"/>
+      <c r="B38" s="191"/>
+      <c r="C38" s="191"/>
+      <c r="D38" s="191"/>
+      <c r="E38" s="193"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="189"/>
-      <c r="B39" s="189"/>
-      <c r="C39" s="189"/>
-      <c r="D39" s="189"/>
-      <c r="E39" s="191"/>
+      <c r="A39" s="191"/>
+      <c r="B39" s="191"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="191"/>
+      <c r="E39" s="193"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="189"/>
-      <c r="B40" s="189"/>
-      <c r="C40" s="189"/>
-      <c r="D40" s="189"/>
-      <c r="E40" s="191"/>
+      <c r="A40" s="191"/>
+      <c r="B40" s="191"/>
+      <c r="C40" s="191"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="193"/>
     </row>
     <row r="41" ht="15.6" spans="1:9">
-      <c r="A41" s="217" t="s">
+      <c r="A41" s="219" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="218"/>
-      <c r="C41" s="218"/>
-      <c r="D41" s="218"/>
-      <c r="E41" s="191"/>
-      <c r="F41" s="219"/>
-      <c r="G41" s="249"/>
-      <c r="H41" s="249"/>
-      <c r="I41" s="332"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="220"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="221"/>
+      <c r="G41" s="251"/>
+      <c r="H41" s="251"/>
+      <c r="I41" s="334"/>
     </row>
     <row r="42" ht="63.15" spans="1:9">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="223" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="222" t="s">
+      <c r="B42" s="224" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="250"/>
-      <c r="D42" s="192" t="s">
+      <c r="C42" s="252"/>
+      <c r="D42" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="251" t="s">
+      <c r="E42" s="253" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="251" t="s">
+      <c r="F42" s="253" t="s">
         <v>49</v>
       </c>
-      <c r="G42" s="251" t="s">
+      <c r="G42" s="253" t="s">
         <v>50</v>
       </c>
-      <c r="H42" s="194" t="s">
+      <c r="H42" s="196" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="3"/>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A43" s="252"/>
-      <c r="B43" s="253"/>
-      <c r="C43" s="254"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="256"/>
-      <c r="F43" s="205"/>
-      <c r="G43" s="257">
+      <c r="A43" s="254"/>
+      <c r="B43" s="255"/>
+      <c r="C43" s="256"/>
+      <c r="D43" s="257"/>
+      <c r="E43" s="258"/>
+      <c r="F43" s="207"/>
+      <c r="G43" s="259">
         <v>0.03</v>
       </c>
-      <c r="H43" s="237">
+      <c r="H43" s="239">
         <f>ROUND(E43*F43*(1+G43),2)</f>
         <v>0</v>
       </c>
       <c r="I43" s="3"/>
     </row>
     <row r="44" ht="15.6" spans="1:9">
-      <c r="A44" s="258"/>
-      <c r="B44" s="259"/>
-      <c r="C44" s="260"/>
-      <c r="D44" s="261"/>
-      <c r="E44" s="262"/>
-      <c r="F44" s="263"/>
-      <c r="G44" s="264"/>
-      <c r="H44" s="248">
+      <c r="A44" s="260"/>
+      <c r="B44" s="261"/>
+      <c r="C44" s="262"/>
+      <c r="D44" s="263"/>
+      <c r="E44" s="264"/>
+      <c r="F44" s="265"/>
+      <c r="G44" s="266"/>
+      <c r="H44" s="250">
         <f>ROUND(E44*F44*(1+G44),2)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="334">
+      <c r="I44" s="336">
         <f>SUM(H43:H44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="5:9">
-      <c r="E45" s="265"/>
-      <c r="I45" s="330">
+      <c r="E45" s="267"/>
+      <c r="I45" s="332">
         <f>I44/$G$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" ht="15.6" spans="1:9">
-      <c r="A48" s="266" t="s">
+      <c r="A48" s="268" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="219"/>
-      <c r="C48" s="219"/>
-      <c r="D48" s="219"/>
-      <c r="F48" s="219"/>
-      <c r="G48" s="249"/>
-      <c r="H48" s="249"/>
-      <c r="I48" s="332"/>
+      <c r="B48" s="221"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="251"/>
+      <c r="H48" s="251"/>
+      <c r="I48" s="334"/>
     </row>
     <row r="49" ht="34.35" spans="1:9">
-      <c r="A49" s="267" t="s">
+      <c r="A49" s="269" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="223"/>
-      <c r="D49" s="250"/>
-      <c r="E49" s="251" t="s">
+      <c r="C49" s="225"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="253" t="s">
         <v>54</v>
       </c>
-      <c r="F49" s="251" t="s">
+      <c r="F49" s="253" t="s">
         <v>55</v>
       </c>
-      <c r="G49" s="192" t="s">
+      <c r="G49" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="268" t="s">
+      <c r="H49" s="270" t="s">
         <v>18</v>
       </c>
-      <c r="I49" s="175"/>
-    </row>
-    <row r="50" s="175" customFormat="1" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A50" s="269" t="s">
+      <c r="I49" s="177"/>
+    </row>
+    <row r="50" s="177" customFormat="1" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A50" s="271" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="270"/>
-      <c r="C50" s="271"/>
-      <c r="D50" s="272"/>
-      <c r="E50" s="273"/>
-      <c r="F50" s="274"/>
-      <c r="G50" s="275"/>
-      <c r="H50" s="276"/>
+      <c r="B50" s="272"/>
+      <c r="C50" s="273"/>
+      <c r="D50" s="274"/>
+      <c r="E50" s="275"/>
+      <c r="F50" s="276"/>
+      <c r="G50" s="277"/>
+      <c r="H50" s="278"/>
     </row>
     <row r="51" ht="16.8" spans="1:9">
-      <c r="A51" s="277" t="s">
+      <c r="A51" s="279" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="278"/>
-      <c r="C51" s="279"/>
-      <c r="D51" s="273"/>
-      <c r="E51" s="280"/>
-      <c r="F51" s="281"/>
-      <c r="G51" s="282"/>
-      <c r="H51" s="283">
+      <c r="B51" s="280"/>
+      <c r="C51" s="281"/>
+      <c r="D51" s="275"/>
+      <c r="E51" s="282"/>
+      <c r="F51" s="283"/>
+      <c r="G51" s="284"/>
+      <c r="H51" s="285">
         <f>ROUND(G51*F51,2)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="175"/>
+      <c r="I51" s="177"/>
     </row>
     <row r="52" ht="15.6" spans="1:9">
-      <c r="A52" s="284" t="s">
+      <c r="A52" s="286" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="285">
+      <c r="B52" s="287">
         <v>21.625</v>
       </c>
-      <c r="C52" s="286">
+      <c r="C52" s="288">
         <v>23.75</v>
       </c>
-      <c r="D52" s="286">
+      <c r="D52" s="288">
         <v>13.625</v>
       </c>
-      <c r="E52" s="287"/>
-      <c r="F52" s="288">
+      <c r="E52" s="289"/>
+      <c r="F52" s="290">
         <v>0.5</v>
       </c>
-      <c r="G52" s="289">
+      <c r="G52" s="291">
         <v>11.5748890625</v>
       </c>
-      <c r="H52" s="290">
+      <c r="H52" s="292">
         <f>ROUND(F52*G52,2)</f>
         <v>5.79</v>
       </c>
-      <c r="I52" s="334">
+      <c r="I52" s="336">
         <f>SUM(H50:H52)</f>
         <v>5.79</v>
       </c>
@@ -5777,11 +5782,11 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="291"/>
-      <c r="F53" s="292"/>
+      <c r="E53" s="293"/>
+      <c r="F53" s="294"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
-      <c r="I53" s="330">
+      <c r="I53" s="332">
         <f>I52/$G$68</f>
         <v>0.0342253645651988</v>
       </c>
@@ -5795,608 +5800,608 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="I54" s="330"/>
+      <c r="I54" s="332"/>
     </row>
     <row r="55" ht="16.8" spans="1:10">
-      <c r="A55" s="175"/>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
+      <c r="A55" s="177"/>
+      <c r="B55" s="177"/>
+      <c r="C55" s="177"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
-      <c r="I55" s="175"/>
-      <c r="J55" s="175"/>
+      <c r="I55" s="177"/>
+      <c r="J55" s="177"/>
     </row>
     <row r="56" ht="16.8" spans="1:10">
-      <c r="A56" s="293" t="s">
+      <c r="A56" s="295" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="294"/>
-      <c r="C56" s="294"/>
-      <c r="D56" s="294"/>
-      <c r="E56" s="294"/>
-      <c r="F56" s="294"/>
-      <c r="G56" s="295"/>
-      <c r="H56" s="295"/>
-      <c r="I56" s="294"/>
-      <c r="J56" s="335"/>
+      <c r="B56" s="296"/>
+      <c r="C56" s="296"/>
+      <c r="D56" s="296"/>
+      <c r="E56" s="296"/>
+      <c r="F56" s="296"/>
+      <c r="G56" s="297"/>
+      <c r="H56" s="297"/>
+      <c r="I56" s="296"/>
+      <c r="J56" s="337"/>
     </row>
     <row r="57" ht="17.55" spans="1:9">
-      <c r="A57" s="296" t="s">
+      <c r="A57" s="298" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="297"/>
-      <c r="C57" s="296" t="s">
+      <c r="B57" s="299"/>
+      <c r="C57" s="298" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="296" t="s">
+      <c r="D57" s="298" t="s">
         <v>62</v>
       </c>
-      <c r="E57" s="298"/>
-      <c r="F57" s="299" t="s">
+      <c r="E57" s="300"/>
+      <c r="F57" s="301" t="s">
         <v>63</v>
       </c>
-      <c r="G57" s="267" t="s">
+      <c r="G57" s="269" t="s">
         <v>64</v>
       </c>
-      <c r="H57" s="300" t="s">
+      <c r="H57" s="302" t="s">
         <v>65</v>
       </c>
-      <c r="I57" s="294"/>
+      <c r="I57" s="296"/>
     </row>
     <row r="58" ht="17.55" spans="1:9">
-      <c r="A58" s="301" t="s">
+      <c r="A58" s="303" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="302"/>
-      <c r="C58" s="303">
+      <c r="B58" s="304"/>
+      <c r="C58" s="305">
         <f>B52*C52*D52/1728*F52</f>
         <v>2.02480174877025</v>
       </c>
-      <c r="D58" s="304" t="s">
+      <c r="D58" s="306" t="s">
         <v>67</v>
       </c>
-      <c r="E58" s="305"/>
-      <c r="F58" s="306">
+      <c r="E58" s="307"/>
+      <c r="F58" s="308">
         <v>0.5</v>
       </c>
-      <c r="G58" s="306">
+      <c r="G58" s="308">
         <v>4.3</v>
       </c>
-      <c r="H58" s="306">
+      <c r="H58" s="308">
         <v>15.85</v>
       </c>
-      <c r="I58" s="336" t="s">
+      <c r="I58" s="338" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="59" ht="16.8" spans="1:9">
-      <c r="A59" s="307"/>
-      <c r="B59" s="308"/>
-      <c r="C59" s="309"/>
-      <c r="D59" s="310" t="s">
+      <c r="A59" s="309"/>
+      <c r="B59" s="310"/>
+      <c r="C59" s="311"/>
+      <c r="D59" s="312" t="s">
         <v>68</v>
       </c>
-      <c r="E59" s="311"/>
-      <c r="F59" s="312">
+      <c r="E59" s="313"/>
+      <c r="F59" s="314">
         <f>F58*$C$58</f>
         <v>1.01240087438513</v>
       </c>
-      <c r="G59" s="312">
+      <c r="G59" s="314">
         <f>G58*$C$58</f>
         <v>8.7066475197121</v>
       </c>
-      <c r="H59" s="312">
+      <c r="H59" s="314">
         <f>H58*$C$58</f>
         <v>32.0931077180085</v>
       </c>
-      <c r="I59" s="337">
+      <c r="I59" s="339">
         <f>G59</f>
         <v>8.7066475197121</v>
       </c>
     </row>
     <row r="60" ht="16.8" spans="1:10">
-      <c r="A60" s="175"/>
-      <c r="B60" s="175"/>
-      <c r="C60" s="175"/>
-      <c r="D60" s="175"/>
-      <c r="E60" s="175"/>
-      <c r="F60" s="175"/>
-      <c r="G60" s="175"/>
-      <c r="H60" s="175"/>
-      <c r="I60" s="175"/>
-      <c r="J60" s="175"/>
+      <c r="A60" s="177"/>
+      <c r="B60" s="177"/>
+      <c r="C60" s="177"/>
+      <c r="D60" s="177"/>
+      <c r="E60" s="177"/>
+      <c r="F60" s="177"/>
+      <c r="G60" s="177"/>
+      <c r="H60" s="177"/>
+      <c r="I60" s="177"/>
+      <c r="J60" s="177"/>
     </row>
     <row r="61" ht="16.8" spans="1:10">
-      <c r="A61" s="175"/>
-      <c r="B61" s="175"/>
-      <c r="C61" s="175"/>
-      <c r="D61" s="175"/>
-      <c r="E61" s="175"/>
-      <c r="F61" s="175"/>
-      <c r="G61" s="175"/>
-      <c r="H61" s="175"/>
-      <c r="I61" s="175"/>
-      <c r="J61" s="175"/>
+      <c r="A61" s="177"/>
+      <c r="B61" s="177"/>
+      <c r="C61" s="177"/>
+      <c r="D61" s="177"/>
+      <c r="E61" s="177"/>
+      <c r="F61" s="177"/>
+      <c r="G61" s="177"/>
+      <c r="H61" s="177"/>
+      <c r="I61" s="177"/>
+      <c r="J61" s="177"/>
     </row>
     <row r="62" ht="16.8" spans="1:10">
-      <c r="A62" s="313" t="s">
+      <c r="A62" s="315" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="175"/>
-      <c r="C62" s="175"/>
-      <c r="D62" s="175"/>
-      <c r="E62" s="175"/>
-      <c r="F62" s="175"/>
-      <c r="G62" s="175"/>
-      <c r="H62" s="175"/>
-      <c r="I62" s="175"/>
-      <c r="J62" s="175"/>
+      <c r="B62" s="177"/>
+      <c r="C62" s="177"/>
+      <c r="D62" s="177"/>
+      <c r="E62" s="177"/>
+      <c r="F62" s="177"/>
+      <c r="G62" s="177"/>
+      <c r="H62" s="177"/>
+      <c r="I62" s="177"/>
+      <c r="J62" s="177"/>
     </row>
     <row r="63" ht="16.8" spans="1:10">
-      <c r="A63" s="314" t="s">
+      <c r="A63" s="316" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="315" t="s">
+      <c r="B63" s="317" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="316"/>
-      <c r="D63" s="316"/>
-      <c r="E63" s="316"/>
-      <c r="F63" s="316"/>
-      <c r="G63" s="317" t="s">
+      <c r="C63" s="318"/>
+      <c r="D63" s="318"/>
+      <c r="E63" s="318"/>
+      <c r="F63" s="318"/>
+      <c r="G63" s="319" t="s">
         <v>72</v>
       </c>
-      <c r="H63" s="318"/>
+      <c r="H63" s="320"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="338"/>
+      <c r="J63" s="340"/>
     </row>
     <row r="64" ht="16.8" spans="1:10">
-      <c r="A64" s="319"/>
-      <c r="B64" s="320"/>
-      <c r="C64" s="321"/>
-      <c r="D64" s="321"/>
-      <c r="E64" s="321"/>
-      <c r="F64" s="321"/>
-      <c r="G64" s="322"/>
-      <c r="H64" s="323"/>
+      <c r="A64" s="321"/>
+      <c r="B64" s="322"/>
+      <c r="C64" s="323"/>
+      <c r="D64" s="323"/>
+      <c r="E64" s="323"/>
+      <c r="F64" s="323"/>
+      <c r="G64" s="324"/>
+      <c r="H64" s="325"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="338"/>
+      <c r="J64" s="340"/>
     </row>
     <row r="65" ht="16.8" spans="1:10">
-      <c r="A65" s="175"/>
-      <c r="B65" s="175"/>
-      <c r="C65" s="175"/>
-      <c r="D65" s="175"/>
-      <c r="E65" s="175"/>
-      <c r="F65" s="175"/>
-      <c r="G65" s="175"/>
-      <c r="H65" s="175"/>
-      <c r="I65" s="175"/>
-      <c r="J65" s="175"/>
+      <c r="A65" s="177"/>
+      <c r="B65" s="177"/>
+      <c r="C65" s="177"/>
+      <c r="D65" s="177"/>
+      <c r="E65" s="177"/>
+      <c r="F65" s="177"/>
+      <c r="G65" s="177"/>
+      <c r="H65" s="177"/>
+      <c r="I65" s="177"/>
+      <c r="J65" s="177"/>
     </row>
     <row r="66" ht="17.55" spans="1:10">
-      <c r="A66" s="175"/>
-      <c r="B66" s="175"/>
-      <c r="C66" s="175"/>
-      <c r="D66" s="175"/>
-      <c r="E66" s="175"/>
-      <c r="F66" s="175"/>
-      <c r="G66" s="175"/>
-      <c r="H66" s="175"/>
-      <c r="I66" s="175"/>
-      <c r="J66" s="175"/>
+      <c r="A66" s="177"/>
+      <c r="B66" s="177"/>
+      <c r="C66" s="177"/>
+      <c r="D66" s="177"/>
+      <c r="E66" s="177"/>
+      <c r="F66" s="177"/>
+      <c r="G66" s="177"/>
+      <c r="H66" s="177"/>
+      <c r="I66" s="177"/>
+      <c r="J66" s="177"/>
     </row>
     <row r="67" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A67" s="339" t="s">
+      <c r="A67" s="341" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="340" t="s">
+      <c r="B67" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="C67" s="340" t="s">
+      <c r="C67" s="342" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="341"/>
-      <c r="E67" s="342" t="s">
+      <c r="D67" s="343"/>
+      <c r="E67" s="344" t="s">
         <v>15</v>
       </c>
-      <c r="F67" s="343" t="s">
+      <c r="F67" s="345" t="s">
         <v>63</v>
       </c>
-      <c r="G67" s="340" t="s">
+      <c r="G67" s="342" t="s">
         <v>64</v>
       </c>
-      <c r="H67" s="344" t="s">
+      <c r="H67" s="346" t="s">
         <v>65</v>
       </c>
       <c r="I67" s="3"/>
-      <c r="J67" s="175"/>
+      <c r="J67" s="177"/>
     </row>
     <row r="68" ht="26.25" customHeight="1" spans="1:13">
-      <c r="A68" s="345"/>
-      <c r="B68" s="346" t="str">
+      <c r="A68" s="347"/>
+      <c r="B68" s="348" t="str">
         <f>A58</f>
         <v>Jakarta ID / HK</v>
       </c>
-      <c r="C68" s="347" t="s">
+      <c r="C68" s="349" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="348"/>
-      <c r="E68" s="349" t="s">
+      <c r="D68" s="350"/>
+      <c r="E68" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="F68" s="350">
+      <c r="F68" s="352">
         <f>$I$17+$I$36+$I$44+$I$52+F59</f>
         <v>161.478531309168</v>
       </c>
-      <c r="G68" s="350">
+      <c r="G68" s="352">
         <f>$I$17+$I$36+$I$44+$I$52+G59</f>
         <v>169.172777954495</v>
       </c>
-      <c r="H68" s="350">
+      <c r="H68" s="352">
         <f>$I$17+$I$36+$I$44+$I$52+H59</f>
         <v>192.559238152791</v>
       </c>
       <c r="I68" s="3"/>
-      <c r="L68" s="175"/>
-      <c r="M68" s="175"/>
+      <c r="L68" s="177"/>
+      <c r="M68" s="177"/>
     </row>
     <row r="69" ht="26.25" customHeight="1" spans="1:9">
-      <c r="A69" s="345"/>
-      <c r="B69" s="351"/>
-      <c r="C69" s="352"/>
-      <c r="D69" s="353"/>
-      <c r="E69" s="354"/>
-      <c r="F69" s="355">
+      <c r="A69" s="347"/>
+      <c r="B69" s="353"/>
+      <c r="C69" s="354"/>
+      <c r="D69" s="355"/>
+      <c r="E69" s="356"/>
+      <c r="F69" s="357">
         <f>ROUND(F68/7.76,3)</f>
         <v>20.809</v>
       </c>
-      <c r="G69" s="355">
+      <c r="G69" s="357">
         <f>ROUND(G68/7.76,3)</f>
         <v>21.801</v>
       </c>
-      <c r="H69" s="356">
+      <c r="H69" s="358">
         <f>ROUND(H68/7.76,3)</f>
         <v>24.814</v>
       </c>
       <c r="I69" s="3"/>
     </row>
     <row r="70" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A70" s="345"/>
-      <c r="B70" s="351"/>
-      <c r="C70" s="357"/>
-      <c r="D70" s="358"/>
-      <c r="E70" s="349" t="s">
+      <c r="A70" s="347"/>
+      <c r="B70" s="353"/>
+      <c r="C70" s="359"/>
+      <c r="D70" s="360"/>
+      <c r="E70" s="351" t="s">
         <v>78</v>
       </c>
-      <c r="F70" s="359">
+      <c r="F70" s="361">
         <v>160.671138652622</v>
       </c>
-      <c r="G70" s="359">
+      <c r="G70" s="361">
         <v>168.326914064723</v>
       </c>
-      <c r="H70" s="350">
+      <c r="H70" s="352">
         <v>191.596441962027</v>
       </c>
       <c r="I70" s="3"/>
-      <c r="J70" s="175"/>
+      <c r="J70" s="177"/>
     </row>
     <row r="71" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A71" s="345"/>
-      <c r="B71" s="351"/>
-      <c r="C71" s="352"/>
-      <c r="D71" s="353"/>
-      <c r="E71" s="354"/>
-      <c r="F71" s="355">
+      <c r="A71" s="347"/>
+      <c r="B71" s="353"/>
+      <c r="C71" s="354"/>
+      <c r="D71" s="355"/>
+      <c r="E71" s="356"/>
+      <c r="F71" s="357">
         <f t="shared" ref="F71:H71" si="2">ROUND(F70/7.76,3)</f>
         <v>20.705</v>
       </c>
-      <c r="G71" s="355">
+      <c r="G71" s="357">
         <f t="shared" si="2"/>
         <v>21.692</v>
       </c>
-      <c r="H71" s="356">
+      <c r="H71" s="358">
         <f t="shared" si="2"/>
         <v>24.69</v>
       </c>
       <c r="I71" s="3"/>
-      <c r="J71" s="175"/>
+      <c r="J71" s="177"/>
     </row>
     <row r="72" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A72" s="345"/>
-      <c r="B72" s="351"/>
-      <c r="C72" s="357"/>
-      <c r="D72" s="358"/>
-      <c r="E72" s="349" t="s">
+      <c r="A72" s="347"/>
+      <c r="B72" s="353"/>
+      <c r="C72" s="359"/>
+      <c r="D72" s="360"/>
+      <c r="E72" s="351" t="s">
         <v>79</v>
       </c>
-      <c r="F72" s="359">
+      <c r="F72" s="361">
         <v>159.863745996076</v>
       </c>
-      <c r="G72" s="359">
+      <c r="G72" s="361">
         <v>167.48105017495</v>
       </c>
-      <c r="H72" s="350">
+      <c r="H72" s="352">
         <v>190.633645771263</v>
       </c>
       <c r="I72" s="3"/>
-      <c r="J72" s="175"/>
+      <c r="J72" s="177"/>
     </row>
     <row r="73" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A73" s="345"/>
-      <c r="B73" s="351"/>
-      <c r="C73" s="352"/>
-      <c r="D73" s="353"/>
-      <c r="E73" s="354"/>
-      <c r="F73" s="355">
+      <c r="A73" s="347"/>
+      <c r="B73" s="353"/>
+      <c r="C73" s="354"/>
+      <c r="D73" s="355"/>
+      <c r="E73" s="356"/>
+      <c r="F73" s="357">
         <f t="shared" ref="F73:H73" si="3">ROUND(F72/7.76,3)</f>
         <v>20.601</v>
       </c>
-      <c r="G73" s="355">
+      <c r="G73" s="357">
         <f t="shared" si="3"/>
         <v>21.583</v>
       </c>
-      <c r="H73" s="356">
+      <c r="H73" s="358">
         <f t="shared" si="3"/>
         <v>24.566</v>
       </c>
       <c r="I73" s="3"/>
-      <c r="J73" s="175"/>
+      <c r="J73" s="177"/>
     </row>
     <row r="74" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A74" s="345"/>
-      <c r="B74" s="351"/>
-      <c r="C74" s="357"/>
-      <c r="D74" s="358"/>
-      <c r="E74" s="349" t="s">
+      <c r="A74" s="347"/>
+      <c r="B74" s="353"/>
+      <c r="C74" s="359"/>
+      <c r="D74" s="360"/>
+      <c r="E74" s="351" t="s">
         <v>80</v>
       </c>
-      <c r="F74" s="359">
+      <c r="F74" s="361">
         <v>159.05635333953</v>
       </c>
-      <c r="G74" s="359">
+      <c r="G74" s="361">
         <v>166.635186285178</v>
       </c>
-      <c r="H74" s="350">
+      <c r="H74" s="352">
         <v>189.670849580499</v>
       </c>
       <c r="I74" s="3"/>
-      <c r="J74" s="175"/>
+      <c r="J74" s="177"/>
     </row>
     <row r="75" ht="26.25" customHeight="1" spans="1:10">
-      <c r="A75" s="360"/>
-      <c r="B75" s="361"/>
-      <c r="C75" s="362"/>
-      <c r="D75" s="363"/>
-      <c r="E75" s="354"/>
-      <c r="F75" s="355">
+      <c r="A75" s="362"/>
+      <c r="B75" s="363"/>
+      <c r="C75" s="364"/>
+      <c r="D75" s="365"/>
+      <c r="E75" s="356"/>
+      <c r="F75" s="357">
         <f t="shared" ref="F75:H75" si="4">ROUND(F74/7.76,3)</f>
         <v>20.497</v>
       </c>
-      <c r="G75" s="355">
+      <c r="G75" s="357">
         <f t="shared" si="4"/>
         <v>21.474</v>
       </c>
-      <c r="H75" s="356">
+      <c r="H75" s="358">
         <f t="shared" si="4"/>
         <v>24.442</v>
       </c>
       <c r="I75" s="3"/>
-      <c r="J75" s="175"/>
+      <c r="J75" s="177"/>
     </row>
     <row r="76" ht="16.8" spans="1:10">
-      <c r="A76" s="364"/>
-      <c r="B76" s="364"/>
-      <c r="C76" s="364"/>
-      <c r="D76" s="364"/>
-      <c r="E76" s="364"/>
-      <c r="F76" s="364"/>
-      <c r="G76" s="364"/>
-      <c r="H76" s="364"/>
-      <c r="I76" s="364"/>
-      <c r="J76" s="364"/>
+      <c r="A76" s="366"/>
+      <c r="B76" s="366"/>
+      <c r="C76" s="366"/>
+      <c r="D76" s="366"/>
+      <c r="E76" s="366"/>
+      <c r="F76" s="366"/>
+      <c r="G76" s="366"/>
+      <c r="H76" s="366"/>
+      <c r="I76" s="366"/>
+      <c r="J76" s="366"/>
     </row>
     <row r="77" ht="16.8" spans="1:10">
-      <c r="A77" s="364"/>
-      <c r="B77" s="364"/>
-      <c r="C77" s="364"/>
-      <c r="D77" s="364"/>
-      <c r="E77" s="364"/>
-      <c r="F77" s="364"/>
-      <c r="G77" s="364"/>
-      <c r="H77" s="364"/>
-      <c r="I77" s="364"/>
-      <c r="J77" s="364"/>
+      <c r="A77" s="366"/>
+      <c r="B77" s="366"/>
+      <c r="C77" s="366"/>
+      <c r="D77" s="366"/>
+      <c r="E77" s="366"/>
+      <c r="F77" s="366"/>
+      <c r="G77" s="366"/>
+      <c r="H77" s="366"/>
+      <c r="I77" s="366"/>
+      <c r="J77" s="366"/>
     </row>
     <row r="78" ht="16.8" spans="1:10">
-      <c r="A78" s="365"/>
-      <c r="B78" s="365"/>
-      <c r="C78" s="365"/>
-      <c r="D78" s="365"/>
-      <c r="E78" s="365"/>
-      <c r="F78" s="365"/>
-      <c r="G78" s="365"/>
-      <c r="H78" s="365"/>
-      <c r="I78" s="365"/>
-      <c r="J78" s="364"/>
+      <c r="A78" s="367"/>
+      <c r="B78" s="367"/>
+      <c r="C78" s="367"/>
+      <c r="D78" s="367"/>
+      <c r="E78" s="367"/>
+      <c r="F78" s="367"/>
+      <c r="G78" s="367"/>
+      <c r="H78" s="367"/>
+      <c r="I78" s="367"/>
+      <c r="J78" s="366"/>
     </row>
     <row r="79" ht="16.8" spans="1:10">
-      <c r="A79" s="366" t="s">
+      <c r="A79" s="368" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="367"/>
-      <c r="C79" s="367"/>
-      <c r="D79" s="367"/>
-      <c r="E79" s="367"/>
-      <c r="F79" s="367"/>
-      <c r="G79" s="367"/>
-      <c r="H79" s="367"/>
-      <c r="I79" s="367"/>
-      <c r="J79" s="390"/>
+      <c r="B79" s="369"/>
+      <c r="C79" s="369"/>
+      <c r="D79" s="369"/>
+      <c r="E79" s="369"/>
+      <c r="F79" s="369"/>
+      <c r="G79" s="369"/>
+      <c r="H79" s="369"/>
+      <c r="I79" s="369"/>
+      <c r="J79" s="392"/>
     </row>
     <row r="80" ht="27.75" customHeight="1" spans="1:10">
-      <c r="A80" s="368" t="s">
+      <c r="A80" s="370" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="369" t="s">
+      <c r="B80" s="371" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="369" t="s">
+      <c r="C80" s="372"/>
+      <c r="D80" s="371" t="s">
         <v>83</v>
       </c>
-      <c r="E80" s="370"/>
-      <c r="F80" s="371" t="s">
+      <c r="E80" s="372"/>
+      <c r="F80" s="373" t="s">
         <v>84</v>
       </c>
-      <c r="G80" s="372"/>
-      <c r="H80" s="373" t="s">
+      <c r="G80" s="374"/>
+      <c r="H80" s="375" t="s">
         <v>85</v>
       </c>
-      <c r="I80" s="391"/>
-      <c r="J80" s="392" t="s">
+      <c r="I80" s="393"/>
+      <c r="J80" s="394" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="81" ht="36.75" customHeight="1" spans="1:10">
-      <c r="A81" s="374" t="str">
+      <c r="A81" s="376" t="str">
         <f>B68</f>
         <v>Jakarta ID / HK</v>
       </c>
-      <c r="B81" s="375"/>
-      <c r="C81" s="376"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="376"/>
-      <c r="F81" s="375"/>
-      <c r="G81" s="376"/>
-      <c r="H81" s="377"/>
-      <c r="I81" s="393"/>
-      <c r="J81" s="394"/>
+      <c r="B81" s="377"/>
+      <c r="C81" s="378"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="378"/>
+      <c r="F81" s="377"/>
+      <c r="G81" s="378"/>
+      <c r="H81" s="379"/>
+      <c r="I81" s="395"/>
+      <c r="J81" s="396"/>
     </row>
     <row r="82" ht="47.25" customHeight="1" spans="1:10">
-      <c r="A82" s="378" t="s">
+      <c r="A82" s="380" t="s">
         <v>63</v>
       </c>
-      <c r="B82" s="379"/>
-      <c r="C82" s="380"/>
-      <c r="D82" s="379"/>
-      <c r="E82" s="380"/>
-      <c r="F82" s="379"/>
-      <c r="G82" s="380"/>
-      <c r="H82" s="381"/>
-      <c r="I82" s="305"/>
-      <c r="J82" s="395"/>
+      <c r="B82" s="381"/>
+      <c r="C82" s="382"/>
+      <c r="D82" s="381"/>
+      <c r="E82" s="382"/>
+      <c r="F82" s="381"/>
+      <c r="G82" s="382"/>
+      <c r="H82" s="383"/>
+      <c r="I82" s="307"/>
+      <c r="J82" s="397"/>
     </row>
     <row r="83" ht="47.25" customHeight="1" spans="1:10">
-      <c r="A83" s="382" t="s">
+      <c r="A83" s="384" t="s">
         <v>64</v>
       </c>
-      <c r="B83" s="379"/>
-      <c r="C83" s="380"/>
-      <c r="D83" s="379"/>
-      <c r="E83" s="380"/>
-      <c r="F83" s="379"/>
-      <c r="G83" s="380"/>
-      <c r="H83" s="383"/>
-      <c r="I83" s="396"/>
-      <c r="J83" s="397" t="s">
+      <c r="B83" s="381"/>
+      <c r="C83" s="382"/>
+      <c r="D83" s="381"/>
+      <c r="E83" s="382"/>
+      <c r="F83" s="381"/>
+      <c r="G83" s="382"/>
+      <c r="H83" s="385"/>
+      <c r="I83" s="398"/>
+      <c r="J83" s="399" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="84" ht="47.25" customHeight="1" spans="1:10">
-      <c r="A84" s="384" t="s">
+      <c r="A84" s="386" t="s">
         <v>65</v>
       </c>
-      <c r="B84" s="379"/>
-      <c r="C84" s="380"/>
-      <c r="D84" s="379"/>
-      <c r="E84" s="380"/>
-      <c r="F84" s="379"/>
-      <c r="G84" s="380"/>
-      <c r="H84" s="385" t="s">
+      <c r="B84" s="381"/>
+      <c r="C84" s="382"/>
+      <c r="D84" s="381"/>
+      <c r="E84" s="382"/>
+      <c r="F84" s="381"/>
+      <c r="G84" s="382"/>
+      <c r="H84" s="387" t="s">
         <v>88</v>
       </c>
-      <c r="I84" s="398"/>
-      <c r="J84" s="395"/>
+      <c r="I84" s="400"/>
+      <c r="J84" s="397"/>
     </row>
     <row r="85" ht="16.8" spans="1:10">
-      <c r="A85" s="386" t="s">
+      <c r="A85" s="388" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="365"/>
-      <c r="C85" s="387"/>
-      <c r="D85" s="387"/>
-      <c r="E85" s="387"/>
-      <c r="F85" s="387"/>
-      <c r="G85" s="387"/>
-      <c r="H85" s="387"/>
-      <c r="I85" s="365"/>
-      <c r="J85" s="364"/>
+      <c r="B85" s="367"/>
+      <c r="C85" s="389"/>
+      <c r="D85" s="389"/>
+      <c r="E85" s="389"/>
+      <c r="F85" s="389"/>
+      <c r="G85" s="389"/>
+      <c r="H85" s="389"/>
+      <c r="I85" s="367"/>
+      <c r="J85" s="366"/>
     </row>
     <row r="86" ht="16.8" spans="1:10">
-      <c r="A86" s="386"/>
-      <c r="B86" s="365"/>
-      <c r="C86" s="387"/>
-      <c r="D86" s="387"/>
-      <c r="E86" s="387"/>
-      <c r="F86" s="387"/>
-      <c r="G86" s="387"/>
-      <c r="H86" s="387"/>
-      <c r="I86" s="365"/>
-      <c r="J86" s="364"/>
+      <c r="A86" s="388"/>
+      <c r="B86" s="367"/>
+      <c r="C86" s="389"/>
+      <c r="D86" s="389"/>
+      <c r="E86" s="389"/>
+      <c r="F86" s="389"/>
+      <c r="G86" s="389"/>
+      <c r="H86" s="389"/>
+      <c r="I86" s="367"/>
+      <c r="J86" s="366"/>
     </row>
     <row r="87" ht="16.8" spans="1:10">
-      <c r="A87" s="388" t="s">
+      <c r="A87" s="390" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="365"/>
-      <c r="C87" s="387"/>
-      <c r="D87" s="387"/>
-      <c r="E87" s="387"/>
-      <c r="F87" s="387"/>
-      <c r="G87" s="387"/>
-      <c r="H87" s="175"/>
-      <c r="I87" s="175"/>
-      <c r="J87" s="364"/>
+      <c r="B87" s="367"/>
+      <c r="C87" s="389"/>
+      <c r="D87" s="389"/>
+      <c r="E87" s="389"/>
+      <c r="F87" s="389"/>
+      <c r="G87" s="389"/>
+      <c r="H87" s="177"/>
+      <c r="I87" s="177"/>
+      <c r="J87" s="366"/>
     </row>
     <row r="88" ht="16.8" spans="1:10">
-      <c r="A88" s="175"/>
-      <c r="B88" s="338"/>
-      <c r="C88" s="338"/>
-      <c r="D88" s="338"/>
-      <c r="E88" s="338"/>
-      <c r="F88" s="338"/>
-      <c r="G88" s="338"/>
-      <c r="H88" s="338"/>
-      <c r="I88" s="338"/>
-      <c r="J88" s="364"/>
+      <c r="A88" s="177"/>
+      <c r="B88" s="340"/>
+      <c r="C88" s="340"/>
+      <c r="D88" s="340"/>
+      <c r="E88" s="340"/>
+      <c r="F88" s="340"/>
+      <c r="G88" s="340"/>
+      <c r="H88" s="340"/>
+      <c r="I88" s="340"/>
+      <c r="J88" s="366"/>
     </row>
     <row r="89" ht="16.8" spans="1:10">
-      <c r="A89" s="389"/>
-      <c r="B89" s="365"/>
-      <c r="C89" s="365"/>
-      <c r="D89" s="365"/>
-      <c r="E89" s="365"/>
-      <c r="F89" s="365"/>
-      <c r="G89" s="365"/>
-      <c r="H89" s="338"/>
-      <c r="I89" s="338"/>
-      <c r="J89" s="364"/>
+      <c r="A89" s="391"/>
+      <c r="B89" s="367"/>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
+      <c r="G89" s="367"/>
+      <c r="H89" s="340"/>
+      <c r="I89" s="340"/>
+      <c r="J89" s="366"/>
     </row>
     <row r="90" ht="16.8" spans="1:10">
-      <c r="A90" s="365"/>
-      <c r="B90" s="365"/>
-      <c r="C90" s="365"/>
-      <c r="D90" s="365"/>
-      <c r="E90" s="365"/>
-      <c r="F90" s="365"/>
-      <c r="G90" s="365"/>
-      <c r="H90" s="338"/>
-      <c r="I90" s="338"/>
-      <c r="J90" s="364"/>
+      <c r="A90" s="367"/>
+      <c r="B90" s="367"/>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
+      <c r="G90" s="367"/>
+      <c r="H90" s="340"/>
+      <c r="I90" s="340"/>
+      <c r="J90" s="366"/>
     </row>
   </sheetData>
   <mergeCells count="68">
@@ -6704,7 +6709,7 @@
       <c r="C15" s="50"/>
       <c r="D15" s="51">
         <f>$G$94</f>
-        <v>20.4910439310689</v>
+        <v>20.491043931069</v>
       </c>
       <c r="E15" s="52">
         <v>0.18</v>
@@ -7891,7 +7896,7 @@
       <c r="F91" s="109"/>
       <c r="G91" s="105">
         <f>SUM(F67:F90)</f>
-        <v>20.4910439310689</v>
+        <v>20.491043931069</v>
       </c>
     </row>
     <row r="92" s="6" customFormat="1" ht="15.6" spans="1:7">
@@ -7927,7 +7932,7 @@
       <c r="F94" s="145"/>
       <c r="G94" s="123">
         <f>SUM(G64:G93)</f>
-        <v>20.4910439310689</v>
+        <v>20.491043931069</v>
       </c>
     </row>
     <row r="95" s="6" customFormat="1" ht="15.6" spans="1:7">
@@ -8027,14 +8032,12 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="92"/>
-      <c r="H101" s="3" t="s">
-        <v>203</v>
-      </c>
+      <c r="H101" s="3"/>
     </row>
     <row r="102" s="6" customFormat="1" ht="15.6" spans="1:8">
       <c r="A102" s="82"/>
       <c r="B102" s="89" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C102" s="150" t="s">
         <v>202</v>
@@ -8050,9 +8053,7 @@
         <v>3.2</v>
       </c>
       <c r="G102" s="92"/>
-      <c r="H102" s="3" t="s">
-        <v>203</v>
-      </c>
+      <c r="H102" s="3"/>
     </row>
     <row r="103" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A103" s="82"/>
@@ -8084,7 +8085,7 @@
         <v>2</v>
       </c>
       <c r="B105" s="83" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C105" s="84"/>
       <c r="D105" s="151"/>
@@ -8145,7 +8146,7 @@
         <v>3</v>
       </c>
       <c r="B111" s="83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C111" s="84"/>
       <c r="D111" s="85"/>
@@ -8165,10 +8166,10 @@
     <row r="113" s="7" customFormat="1" ht="18" customHeight="1" spans="1:7">
       <c r="A113" s="82"/>
       <c r="B113" s="89" t="s">
+        <v>206</v>
+      </c>
+      <c r="C113" s="150" t="s">
         <v>207</v>
-      </c>
-      <c r="C113" s="150" t="s">
-        <v>208</v>
       </c>
       <c r="D113" s="153">
         <v>4</v>
@@ -8185,7 +8186,7 @@
     <row r="114" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A114" s="82"/>
       <c r="B114" s="89" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C114" s="150" t="s">
         <v>202</v>
@@ -8208,7 +8209,7 @@
     <row r="115" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A115" s="82"/>
       <c r="B115" s="89" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C115" s="150" t="s">
         <v>202</v>
@@ -8231,10 +8232,10 @@
     <row r="116" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A116" s="82"/>
       <c r="B116" s="139" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C116" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D116" s="153">
         <v>8</v>
@@ -8254,10 +8255,10 @@
     <row r="117" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A117" s="82"/>
       <c r="B117" s="139" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C117" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D117" s="153">
         <v>4</v>
@@ -8277,10 +8278,10 @@
     <row r="118" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A118" s="82"/>
       <c r="B118" s="139" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C118" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D118" s="153">
         <v>2</v>
@@ -8300,7 +8301,7 @@
     <row r="119" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A119" s="82"/>
       <c r="B119" s="139" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C119" s="150" t="s">
         <v>202</v>
@@ -8323,7 +8324,7 @@
     <row r="120" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A120" s="82"/>
       <c r="B120" s="139" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C120" s="150" t="s">
         <v>202</v>
@@ -8346,7 +8347,7 @@
     <row r="121" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A121" s="82"/>
       <c r="B121" s="139" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C121" s="150" t="s">
         <v>202</v>
@@ -8369,10 +8370,10 @@
     <row r="122" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A122" s="82"/>
       <c r="B122" s="139" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C122" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D122" s="153">
         <v>83</v>
@@ -8392,10 +8393,10 @@
     <row r="123" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A123" s="82"/>
       <c r="B123" s="139" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C123" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D123" s="153">
         <v>6</v>
@@ -8415,10 +8416,10 @@
     <row r="124" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A124" s="82"/>
       <c r="B124" s="139" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C124" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D124" s="153">
         <v>14</v>
@@ -8438,10 +8439,10 @@
     <row r="125" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A125" s="82"/>
       <c r="B125" s="139" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C125" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D125" s="153">
         <v>8</v>
@@ -8461,7 +8462,7 @@
     <row r="126" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A126" s="82"/>
       <c r="B126" s="89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C126" s="150" t="s">
         <v>202</v>
@@ -8484,7 +8485,7 @@
     <row r="127" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A127" s="82"/>
       <c r="B127" s="89" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C127" s="150" t="s">
         <v>202</v>
@@ -8507,10 +8508,10 @@
     <row r="128" s="7" customFormat="1" ht="18" customHeight="1" spans="1:7">
       <c r="A128" s="82"/>
       <c r="B128" s="139" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C128" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D128" s="153">
         <v>3</v>
@@ -8527,7 +8528,7 @@
     <row r="129" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A129" s="82"/>
       <c r="B129" s="139" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C129" s="150" t="s">
         <v>202</v>
@@ -8550,7 +8551,7 @@
     <row r="130" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A130" s="82"/>
       <c r="B130" s="139" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C130" s="150" t="s">
         <v>202</v>
@@ -8573,10 +8574,10 @@
     <row r="131" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A131" s="82"/>
       <c r="B131" s="139" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C131" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D131" s="153">
         <v>2</v>
@@ -8596,10 +8597,10 @@
     <row r="132" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A132" s="82"/>
       <c r="B132" s="139" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C132" s="150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D132" s="153">
         <v>2</v>
@@ -8660,7 +8661,7 @@
         <v>142</v>
       </c>
       <c r="B137" s="141" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C137" s="142"/>
       <c r="D137" s="143"/>
@@ -8691,7 +8692,7 @@
     </row>
     <row r="140" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A140" s="130" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B140" s="125"/>
       <c r="C140" s="126"/>
@@ -8761,7 +8762,7 @@
         <v>142</v>
       </c>
       <c r="B145" s="163" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C145" s="164"/>
       <c r="D145" s="165"/>
@@ -8792,7 +8793,7 @@
     </row>
     <row r="148" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A148" s="130" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B148" s="125"/>
       <c r="C148" s="126"/>
@@ -8807,10 +8808,10 @@
         <v>101</v>
       </c>
       <c r="C149" s="73" t="s">
+        <v>231</v>
+      </c>
+      <c r="D149" s="73" t="s">
         <v>232</v>
-      </c>
-      <c r="D149" s="73" t="s">
-        <v>233</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>49</v>
@@ -8836,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="B151" s="83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C151" s="85" t="s">
         <v>142</v>
@@ -8853,7 +8854,7 @@
     <row r="152" s="6" customFormat="1" ht="15.6" spans="1:8">
       <c r="A152" s="88"/>
       <c r="B152" s="89" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C152" s="170" t="s">
         <v>202</v>
@@ -8867,10 +8868,10 @@
     <row r="153" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A153" s="88"/>
       <c r="B153" s="89" t="s">
+        <v>235</v>
+      </c>
+      <c r="C153" s="170" t="s">
         <v>236</v>
-      </c>
-      <c r="C153" s="170" t="s">
-        <v>237</v>
       </c>
       <c r="D153" s="96">
         <v>80</v>
@@ -8889,7 +8890,7 @@
     <row r="154" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A154" s="88"/>
       <c r="B154" s="89" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C154" s="170"/>
       <c r="D154" s="96"/>
@@ -8914,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="B156" s="83" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C156" s="170"/>
       <c r="D156" s="96"/>
@@ -8925,10 +8926,10 @@
     <row r="157" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A157" s="82"/>
       <c r="B157" s="89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C157" s="170" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D157" s="96"/>
       <c r="E157" s="92"/>
@@ -8938,10 +8939,10 @@
     <row r="158" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A158" s="82"/>
       <c r="B158" s="89" t="s">
+        <v>240</v>
+      </c>
+      <c r="C158" s="170" t="s">
         <v>241</v>
-      </c>
-      <c r="C158" s="170" t="s">
-        <v>242</v>
       </c>
       <c r="D158" s="96"/>
       <c r="E158" s="92"/>
@@ -8965,10 +8966,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="83" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C160" s="170" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D160" s="96"/>
       <c r="E160" s="92"/>
@@ -8992,10 +8993,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="83" t="s">
+        <v>243</v>
+      </c>
+      <c r="C162" s="170" t="s">
         <v>244</v>
-      </c>
-      <c r="C162" s="170" t="s">
-        <v>245</v>
       </c>
       <c r="D162" s="96"/>
       <c r="E162" s="92"/>
@@ -9019,7 +9020,7 @@
         <v>5</v>
       </c>
       <c r="B164" s="83" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C164" s="170"/>
       <c r="D164" s="96"/>
@@ -9030,10 +9031,10 @@
     <row r="165" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A165" s="82"/>
       <c r="B165" s="89" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C165" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D165" s="96">
         <v>11</v>
@@ -9050,10 +9051,10 @@
     <row r="166" s="6" customFormat="1" ht="15.6" spans="1:8">
       <c r="A166" s="82"/>
       <c r="B166" s="89" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C166" s="170" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D166" s="96"/>
       <c r="E166" s="92"/>
@@ -9064,10 +9065,10 @@
     <row r="167" s="6" customFormat="1" ht="15.6" spans="1:7">
       <c r="A167" s="82"/>
       <c r="B167" s="89" t="s">
+        <v>248</v>
+      </c>
+      <c r="C167" s="170" t="s">
         <v>249</v>
-      </c>
-      <c r="C167" s="170" t="s">
-        <v>250</v>
       </c>
       <c r="D167" s="96"/>
       <c r="E167" s="92"/>
@@ -9099,12 +9100,12 @@
       <c r="A170" s="140" t="s">
         <v>142</v>
       </c>
-      <c r="B170" s="163" t="s">
-        <v>251</v>
-      </c>
-      <c r="C170" s="164"/>
-      <c r="D170" s="164"/>
-      <c r="E170" s="165"/>
+      <c r="B170" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="C170" s="172"/>
+      <c r="D170" s="172"/>
+      <c r="E170" s="173"/>
       <c r="F170" s="157"/>
       <c r="G170" s="123">
         <f>SUM(G151:G169)</f>
@@ -9112,86 +9113,85 @@
       </c>
     </row>
     <row r="171" spans="2:7">
-      <c r="B171" s="172"/>
-      <c r="E171" s="173"/>
-      <c r="F171" s="173"/>
-      <c r="G171" s="173"/>
+      <c r="B171" s="174"/>
+      <c r="E171" s="175"/>
+      <c r="F171" s="175"/>
+      <c r="G171" s="175"/>
     </row>
     <row r="172" spans="2:7">
-      <c r="B172" s="172"/>
-      <c r="E172" s="173"/>
-      <c r="F172" s="173"/>
-      <c r="G172" s="173"/>
+      <c r="B172" s="174"/>
+      <c r="E172" s="175"/>
+      <c r="F172" s="175"/>
+      <c r="G172" s="175"/>
     </row>
     <row r="173" spans="2:7">
-      <c r="B173" s="172"/>
-      <c r="E173" s="173"/>
-      <c r="F173" s="173"/>
-      <c r="G173" s="173"/>
+      <c r="B173" s="174"/>
+      <c r="E173" s="175"/>
+      <c r="F173" s="175"/>
+      <c r="G173" s="175"/>
     </row>
     <row r="174" spans="2:7">
-      <c r="B174" s="172"/>
-      <c r="E174" s="173"/>
-      <c r="F174" s="173"/>
-      <c r="G174" s="173"/>
+      <c r="B174" s="174"/>
+      <c r="E174" s="175"/>
+      <c r="F174" s="175"/>
+      <c r="G174" s="175"/>
     </row>
     <row r="175" spans="2:7">
-      <c r="B175" s="172"/>
-      <c r="E175" s="173"/>
-      <c r="F175" s="173"/>
-      <c r="G175" s="173"/>
+      <c r="B175" s="174"/>
+      <c r="E175" s="175"/>
+      <c r="F175" s="175"/>
+      <c r="G175" s="175"/>
     </row>
     <row r="176" spans="2:7">
-      <c r="B176" s="172"/>
-      <c r="E176" s="173"/>
-      <c r="F176" s="173"/>
-      <c r="G176" s="173"/>
+      <c r="B176" s="174"/>
+      <c r="E176" s="175"/>
+      <c r="F176" s="175"/>
+      <c r="G176" s="175"/>
     </row>
     <row r="177" spans="2:7">
-      <c r="B177" s="172"/>
-      <c r="E177" s="173"/>
-      <c r="F177" s="173"/>
-      <c r="G177" s="173"/>
+      <c r="B177" s="174"/>
+      <c r="E177" s="175"/>
+      <c r="F177" s="175"/>
+      <c r="G177" s="175"/>
     </row>
     <row r="178" spans="2:7">
-      <c r="B178" s="172"/>
-      <c r="E178" s="173"/>
-      <c r="F178" s="173"/>
-      <c r="G178" s="173"/>
+      <c r="B178" s="174"/>
+      <c r="E178" s="175"/>
+      <c r="F178" s="175"/>
+      <c r="G178" s="175"/>
     </row>
     <row r="179" spans="2:7">
-      <c r="B179" s="172"/>
-      <c r="E179" s="173"/>
-      <c r="F179" s="173"/>
-      <c r="G179" s="173"/>
+      <c r="B179" s="174"/>
+      <c r="E179" s="175"/>
+      <c r="F179" s="175"/>
+      <c r="G179" s="175"/>
     </row>
     <row r="180" spans="2:7">
-      <c r="B180" s="172"/>
-      <c r="E180" s="173"/>
-      <c r="F180" s="173"/>
-      <c r="G180" s="173"/>
+      <c r="B180" s="174"/>
+      <c r="E180" s="175"/>
+      <c r="F180" s="175"/>
+      <c r="G180" s="175"/>
     </row>
     <row r="181" spans="2:7">
-      <c r="B181" s="172"/>
-      <c r="E181" s="173"/>
-      <c r="F181" s="173"/>
-      <c r="G181" s="173"/>
+      <c r="B181" s="174"/>
+      <c r="E181" s="175"/>
+      <c r="F181" s="175"/>
+      <c r="G181" s="175"/>
     </row>
     <row r="182" spans="2:7">
-      <c r="B182" s="172"/>
-      <c r="E182" s="173"/>
-      <c r="F182" s="173"/>
-      <c r="G182" s="173"/>
+      <c r="B182" s="174"/>
+      <c r="E182" s="175"/>
+      <c r="F182" s="175"/>
+      <c r="G182" s="175"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B145:D145"/>
-    <mergeCell ref="B170:E170"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.2" bottom="0.7" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="portrait"/>
@@ -9215,17 +9215,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -9235,7 +9235,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
